--- a/Valyuta.xlsx
+++ b/Valyuta.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Valyuta_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3522E369-33A5-4D9D-8264-CD8B6CCC15DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B694BDA6-B3A1-4021-B4EC-E09B85342CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t>Sana</t>
   </si>
@@ -360,12 +357,114 @@
   <si>
     <t>EVRO 
 (978)</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -410,12 +509,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -500,1492 +602,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Worksheet"/>
-      <sheetName val="Лист1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>2025-08-01</v>
-          </cell>
-          <cell r="B3">
-            <v>1</v>
-          </cell>
-          <cell r="C3">
-            <v>12692.42</v>
-          </cell>
-          <cell r="D3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>2025-08-04</v>
-          </cell>
-          <cell r="B4">
-            <v>1</v>
-          </cell>
-          <cell r="C4">
-            <v>12725.16</v>
-          </cell>
-          <cell r="D4">
-            <v>32.739999999999782</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>2025-08-05</v>
-          </cell>
-          <cell r="B5">
-            <v>1</v>
-          </cell>
-          <cell r="C5">
-            <v>12621.29</v>
-          </cell>
-          <cell r="D5">
-            <v>-71.1299999999992</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>2025-08-06</v>
-          </cell>
-          <cell r="B6">
-            <v>1</v>
-          </cell>
-          <cell r="C6">
-            <v>12524.89</v>
-          </cell>
-          <cell r="D6">
-            <v>-167.53000000000065</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>2025-08-07</v>
-          </cell>
-          <cell r="B7">
-            <v>1</v>
-          </cell>
-          <cell r="C7">
-            <v>12502.99</v>
-          </cell>
-          <cell r="D7">
-            <v>-189.43000000000029</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>2025-08-08</v>
-          </cell>
-          <cell r="B8">
-            <v>1</v>
-          </cell>
-          <cell r="C8">
-            <v>12593.77</v>
-          </cell>
-          <cell r="D8">
-            <v>-98.649999999999636</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>2025-08-11</v>
-          </cell>
-          <cell r="B9">
-            <v>1</v>
-          </cell>
-          <cell r="C9">
-            <v>12672.81</v>
-          </cell>
-          <cell r="D9">
-            <v>-19.610000000000582</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>2025-08-12</v>
-          </cell>
-          <cell r="B10">
-            <v>1</v>
-          </cell>
-          <cell r="C10">
-            <v>12589.35</v>
-          </cell>
-          <cell r="D10">
-            <v>-103.06999999999971</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>2025-08-13</v>
-          </cell>
-          <cell r="B11">
-            <v>1</v>
-          </cell>
-          <cell r="C11">
-            <v>12509.83</v>
-          </cell>
-          <cell r="D11">
-            <v>-182.59000000000015</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>2025-08-14</v>
-          </cell>
-          <cell r="B12">
-            <v>1</v>
-          </cell>
-          <cell r="C12">
-            <v>12497.75</v>
-          </cell>
-          <cell r="D12">
-            <v>-194.67000000000007</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>2025-08-15</v>
-          </cell>
-          <cell r="B13">
-            <v>1</v>
-          </cell>
-          <cell r="C13">
-            <v>12581.97</v>
-          </cell>
-          <cell r="D13">
-            <v>-110.45000000000073</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>2025-08-18</v>
-          </cell>
-          <cell r="B14">
-            <v>1</v>
-          </cell>
-          <cell r="C14">
-            <v>12547.38</v>
-          </cell>
-          <cell r="D14">
-            <v>-145.04000000000087</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>2025-08-19</v>
-          </cell>
-          <cell r="B15">
-            <v>1</v>
-          </cell>
-          <cell r="C15">
-            <v>12497.19</v>
-          </cell>
-          <cell r="D15">
-            <v>-195.22999999999956</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>2025-08-20</v>
-          </cell>
-          <cell r="B16">
-            <v>1</v>
-          </cell>
-          <cell r="C16">
-            <v>12524.92</v>
-          </cell>
-          <cell r="D16">
-            <v>-167.5</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>2025-08-21</v>
-          </cell>
-          <cell r="B17">
-            <v>1</v>
-          </cell>
-          <cell r="C17">
-            <v>12466.44</v>
-          </cell>
-          <cell r="D17">
-            <v>-225.97999999999956</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>2025-08-22</v>
-          </cell>
-          <cell r="B18">
-            <v>1</v>
-          </cell>
-          <cell r="C18">
-            <v>12413.79</v>
-          </cell>
-          <cell r="D18">
-            <v>-278.6299999999992</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>2025-08-25</v>
-          </cell>
-          <cell r="B19">
-            <v>1</v>
-          </cell>
-          <cell r="C19">
-            <v>12357.09</v>
-          </cell>
-          <cell r="D19">
-            <v>-335.32999999999993</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>2025-08-26</v>
-          </cell>
-          <cell r="B20">
-            <v>1</v>
-          </cell>
-          <cell r="C20">
-            <v>12305.8</v>
-          </cell>
-          <cell r="D20">
-            <v>-386.6200000000008</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>2025-08-27</v>
-          </cell>
-          <cell r="B21">
-            <v>1</v>
-          </cell>
-          <cell r="C21">
-            <v>12354.65</v>
-          </cell>
-          <cell r="D21">
-            <v>-337.77000000000044</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>2025-08-28</v>
-          </cell>
-          <cell r="B22">
-            <v>1</v>
-          </cell>
-          <cell r="C22">
-            <v>12412.98</v>
-          </cell>
-          <cell r="D22">
-            <v>-279.44000000000051</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>2025-08-29</v>
-          </cell>
-          <cell r="B23">
-            <v>1</v>
-          </cell>
-          <cell r="C23">
-            <v>12482.38</v>
-          </cell>
-          <cell r="D23">
-            <v>-210.04000000000087</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>2025-09-02</v>
-          </cell>
-          <cell r="B24">
-            <v>1</v>
-          </cell>
-          <cell r="C24">
-            <v>12460.7</v>
-          </cell>
-          <cell r="D24">
-            <v>-231.71999999999935</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>2025-09-03</v>
-          </cell>
-          <cell r="B25">
-            <v>1</v>
-          </cell>
-          <cell r="C25">
-            <v>12422.9</v>
-          </cell>
-          <cell r="D25">
-            <v>-269.52000000000044</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>2025-09-04</v>
-          </cell>
-          <cell r="B26">
-            <v>1</v>
-          </cell>
-          <cell r="C26">
-            <v>12374.55</v>
-          </cell>
-          <cell r="D26">
-            <v>-317.8700000000008</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>2025-09-05</v>
-          </cell>
-          <cell r="B27">
-            <v>1</v>
-          </cell>
-          <cell r="C27">
-            <v>12437.15</v>
-          </cell>
-          <cell r="D27">
-            <v>-255.27000000000044</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>2025-09-08</v>
-          </cell>
-          <cell r="B28">
-            <v>1</v>
-          </cell>
-          <cell r="C28">
-            <v>12520.78</v>
-          </cell>
-          <cell r="D28">
-            <v>-171.63999999999942</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>2025-09-09</v>
-          </cell>
-          <cell r="B29">
-            <v>1</v>
-          </cell>
-          <cell r="C29">
-            <v>12439.41</v>
-          </cell>
-          <cell r="D29">
-            <v>-253.01000000000022</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>2025-09-10</v>
-          </cell>
-          <cell r="B30">
-            <v>1</v>
-          </cell>
-          <cell r="C30">
-            <v>12355.14</v>
-          </cell>
-          <cell r="D30">
-            <v>-337.28000000000065</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>2025-09-11</v>
-          </cell>
-          <cell r="B31">
-            <v>1</v>
-          </cell>
-          <cell r="C31">
-            <v>12360.86</v>
-          </cell>
-          <cell r="D31">
-            <v>-331.55999999999949</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>2025-09-12</v>
-          </cell>
-          <cell r="B32">
-            <v>1</v>
-          </cell>
-          <cell r="C32">
-            <v>12447.35</v>
-          </cell>
-          <cell r="D32">
-            <v>-245.06999999999971</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>2025-09-15</v>
-          </cell>
-          <cell r="B33">
-            <v>1</v>
-          </cell>
-          <cell r="C33">
-            <v>12426.83</v>
-          </cell>
-          <cell r="D33">
-            <v>-265.59000000000015</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>2025-09-16</v>
-          </cell>
-          <cell r="B34">
-            <v>1</v>
-          </cell>
-          <cell r="C34">
-            <v>12344.61</v>
-          </cell>
-          <cell r="D34">
-            <v>-347.80999999999949</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>2025-09-17</v>
-          </cell>
-          <cell r="B35">
-            <v>1</v>
-          </cell>
-          <cell r="C35">
-            <v>12285.16</v>
-          </cell>
-          <cell r="D35">
-            <v>-407.26000000000022</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>2025-09-18</v>
-          </cell>
-          <cell r="B36">
-            <v>1</v>
-          </cell>
-          <cell r="C36">
-            <v>12254.27</v>
-          </cell>
-          <cell r="D36">
-            <v>-438.14999999999964</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>2025-09-19</v>
-          </cell>
-          <cell r="B37">
-            <v>1</v>
-          </cell>
-          <cell r="C37">
-            <v>12314.71</v>
-          </cell>
-          <cell r="D37">
-            <v>-377.71000000000095</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>2025-09-22</v>
-          </cell>
-          <cell r="B38">
-            <v>1</v>
-          </cell>
-          <cell r="C38">
-            <v>12349.87</v>
-          </cell>
-          <cell r="D38">
-            <v>-342.54999999999927</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>2025-09-23</v>
-          </cell>
-          <cell r="B39">
-            <v>1</v>
-          </cell>
-          <cell r="C39">
-            <v>12257.13</v>
-          </cell>
-          <cell r="D39">
-            <v>-435.29000000000087</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>2025-09-24</v>
-          </cell>
-          <cell r="B40">
-            <v>1</v>
-          </cell>
-          <cell r="C40">
-            <v>12171.03</v>
-          </cell>
-          <cell r="D40">
-            <v>-521.38999999999942</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>2025-09-25</v>
-          </cell>
-          <cell r="B41">
-            <v>1</v>
-          </cell>
-          <cell r="C41">
-            <v>12219.08</v>
-          </cell>
-          <cell r="D41">
-            <v>-473.34000000000015</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>2025-09-26</v>
-          </cell>
-          <cell r="B42">
-            <v>1</v>
-          </cell>
-          <cell r="C42">
-            <v>12199.71</v>
-          </cell>
-          <cell r="D42">
-            <v>-492.71000000000095</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>2025-09-29</v>
-          </cell>
-          <cell r="B43">
-            <v>1</v>
-          </cell>
-          <cell r="C43">
-            <v>12138.67</v>
-          </cell>
-          <cell r="D43">
-            <v>-553.75</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>2025-09-30</v>
-          </cell>
-          <cell r="B44">
-            <v>1</v>
-          </cell>
-          <cell r="C44">
-            <v>12067.76</v>
-          </cell>
-          <cell r="D44">
-            <v>-624.65999999999985</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>2025-10-02</v>
-          </cell>
-          <cell r="B45">
-            <v>1</v>
-          </cell>
-          <cell r="C45">
-            <v>12084.1</v>
-          </cell>
-          <cell r="D45">
-            <v>-608.31999999999971</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>2025-10-03</v>
-          </cell>
-          <cell r="B46">
-            <v>1</v>
-          </cell>
-          <cell r="C46">
-            <v>12099.72</v>
-          </cell>
-          <cell r="D46">
-            <v>-592.70000000000073</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>2025-10-06</v>
-          </cell>
-          <cell r="B47">
-            <v>1</v>
-          </cell>
-          <cell r="C47">
-            <v>12060.48</v>
-          </cell>
-          <cell r="D47">
-            <v>-631.94000000000051</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>2025-10-07</v>
-          </cell>
-          <cell r="B48">
-            <v>1</v>
-          </cell>
-          <cell r="C48">
-            <v>12022.9</v>
-          </cell>
-          <cell r="D48">
-            <v>-669.52000000000044</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>2025-10-08</v>
-          </cell>
-          <cell r="B49">
-            <v>1</v>
-          </cell>
-          <cell r="C49">
-            <v>12038.68</v>
-          </cell>
-          <cell r="D49">
-            <v>-653.73999999999978</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>2025-10-09</v>
-          </cell>
-          <cell r="B50">
-            <v>1</v>
-          </cell>
-          <cell r="C50">
-            <v>12072.03</v>
-          </cell>
-          <cell r="D50">
-            <v>-620.38999999999942</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>2025-10-10</v>
-          </cell>
-          <cell r="B51">
-            <v>1</v>
-          </cell>
-          <cell r="C51">
-            <v>12123.38</v>
-          </cell>
-          <cell r="D51">
-            <v>-569.04000000000087</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>2025-10-13</v>
-          </cell>
-          <cell r="B52">
-            <v>1</v>
-          </cell>
-          <cell r="C52">
-            <v>12140.91</v>
-          </cell>
-          <cell r="D52">
-            <v>-551.51000000000022</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>2025-10-14</v>
-          </cell>
-          <cell r="B53">
-            <v>1</v>
-          </cell>
-          <cell r="C53">
-            <v>12149.55</v>
-          </cell>
-          <cell r="D53">
-            <v>-542.8700000000008</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v>2025-10-15</v>
-          </cell>
-          <cell r="B54">
-            <v>1</v>
-          </cell>
-          <cell r="C54">
-            <v>12185.11</v>
-          </cell>
-          <cell r="D54">
-            <v>-507.30999999999949</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>2025-10-16</v>
-          </cell>
-          <cell r="B55">
-            <v>1</v>
-          </cell>
-          <cell r="C55">
-            <v>12233.67</v>
-          </cell>
-          <cell r="D55">
-            <v>-458.75</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>2025-10-17</v>
-          </cell>
-          <cell r="B56">
-            <v>1</v>
-          </cell>
-          <cell r="C56">
-            <v>12160.99</v>
-          </cell>
-          <cell r="D56">
-            <v>-531.43000000000029</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>2025-10-20</v>
-          </cell>
-          <cell r="B57">
-            <v>1</v>
-          </cell>
-          <cell r="C57">
-            <v>12108.24</v>
-          </cell>
-          <cell r="D57">
-            <v>-584.18000000000029</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>2025-10-21</v>
-          </cell>
-          <cell r="B58">
-            <v>1</v>
-          </cell>
-          <cell r="C58">
-            <v>12060.15</v>
-          </cell>
-          <cell r="D58">
-            <v>-632.27000000000044</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>2025-10-22</v>
-          </cell>
-          <cell r="B59">
-            <v>1</v>
-          </cell>
-          <cell r="C59">
-            <v>12011.02</v>
-          </cell>
-          <cell r="D59">
-            <v>-681.39999999999964</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60" t="str">
-            <v>2025-10-23</v>
-          </cell>
-          <cell r="B60">
-            <v>1</v>
-          </cell>
-          <cell r="C60">
-            <v>12101.29</v>
-          </cell>
-          <cell r="D60">
-            <v>-591.1299999999992</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61" t="str">
-            <v>2025-10-24</v>
-          </cell>
-          <cell r="B61">
-            <v>1</v>
-          </cell>
-          <cell r="C61">
-            <v>12129.33</v>
-          </cell>
-          <cell r="D61">
-            <v>-563.09000000000015</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62" t="str">
-            <v>2025-10-27</v>
-          </cell>
-          <cell r="B62">
-            <v>1</v>
-          </cell>
-          <cell r="C62">
-            <v>12117.35</v>
-          </cell>
-          <cell r="D62">
-            <v>-575.06999999999971</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63" t="str">
-            <v>2025-10-28</v>
-          </cell>
-          <cell r="B63">
-            <v>1</v>
-          </cell>
-          <cell r="C63">
-            <v>12053.46</v>
-          </cell>
-          <cell r="D63">
-            <v>-638.96000000000095</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64" t="str">
-            <v>2025-10-29</v>
-          </cell>
-          <cell r="B64">
-            <v>1</v>
-          </cell>
-          <cell r="C64">
-            <v>12004.47</v>
-          </cell>
-          <cell r="D64">
-            <v>-687.95000000000073</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65" t="str">
-            <v>2025-10-30</v>
-          </cell>
-          <cell r="B65">
-            <v>1</v>
-          </cell>
-          <cell r="C65">
-            <v>11990.53</v>
-          </cell>
-          <cell r="D65">
-            <v>-701.88999999999942</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66" t="str">
-            <v>2025-10-31</v>
-          </cell>
-          <cell r="B66">
-            <v>1</v>
-          </cell>
-          <cell r="C66">
-            <v>12025.22</v>
-          </cell>
-          <cell r="D66">
-            <v>-667.20000000000073</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67" t="str">
-            <v>2025-11-03</v>
-          </cell>
-          <cell r="B67">
-            <v>1</v>
-          </cell>
-          <cell r="C67">
-            <v>12005.09</v>
-          </cell>
-          <cell r="D67">
-            <v>-687.32999999999993</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68" t="str">
-            <v>2025-11-04</v>
-          </cell>
-          <cell r="B68">
-            <v>1</v>
-          </cell>
-          <cell r="C68">
-            <v>11972.34</v>
-          </cell>
-          <cell r="D68">
-            <v>-720.07999999999993</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69" t="str">
-            <v>2025-11-05</v>
-          </cell>
-          <cell r="B69">
-            <v>1</v>
-          </cell>
-          <cell r="C69">
-            <v>11950.63</v>
-          </cell>
-          <cell r="D69">
-            <v>-741.79000000000087</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70" t="str">
-            <v>2025-11-06</v>
-          </cell>
-          <cell r="B70">
-            <v>1</v>
-          </cell>
-          <cell r="C70">
-            <v>11970.67</v>
-          </cell>
-          <cell r="D70">
-            <v>-721.75</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71" t="str">
-            <v>2025-11-07</v>
-          </cell>
-          <cell r="B71">
-            <v>1</v>
-          </cell>
-          <cell r="C71">
-            <v>12022.92</v>
-          </cell>
-          <cell r="D71">
-            <v>-669.5</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72" t="str">
-            <v>2025-11-10</v>
-          </cell>
-          <cell r="B72">
-            <v>1</v>
-          </cell>
-          <cell r="C72">
-            <v>12060.27</v>
-          </cell>
-          <cell r="D72">
-            <v>-632.14999999999964</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73" t="str">
-            <v>2025-11-11</v>
-          </cell>
-          <cell r="B73">
-            <v>1</v>
-          </cell>
-          <cell r="C73">
-            <v>12014.94</v>
-          </cell>
-          <cell r="D73">
-            <v>-677.47999999999956</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74" t="str">
-            <v>2025-11-12</v>
-          </cell>
-          <cell r="B74">
-            <v>1</v>
-          </cell>
-          <cell r="C74">
-            <v>11990</v>
-          </cell>
-          <cell r="D74">
-            <v>-702.42000000000007</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75" t="str">
-            <v>2025-11-13</v>
-          </cell>
-          <cell r="B75">
-            <v>1</v>
-          </cell>
-          <cell r="C75">
-            <v>11972.35</v>
-          </cell>
-          <cell r="D75">
-            <v>-720.06999999999971</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76" t="str">
-            <v>2025-11-14</v>
-          </cell>
-          <cell r="B76">
-            <v>1</v>
-          </cell>
-          <cell r="C76">
-            <v>11985.1</v>
-          </cell>
-          <cell r="D76">
-            <v>-707.31999999999971</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77" t="str">
-            <v>2025-11-17</v>
-          </cell>
-          <cell r="B77">
-            <v>1</v>
-          </cell>
-          <cell r="C77">
-            <v>12039.61</v>
-          </cell>
-          <cell r="D77">
-            <v>-652.80999999999949</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78" t="str">
-            <v>2025-11-18</v>
-          </cell>
-          <cell r="B78">
-            <v>1</v>
-          </cell>
-          <cell r="C78">
-            <v>12009.92</v>
-          </cell>
-          <cell r="D78">
-            <v>-682.5</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79" t="str">
-            <v>2025-11-19</v>
-          </cell>
-          <cell r="B79">
-            <v>1</v>
-          </cell>
-          <cell r="C79">
-            <v>11940.7</v>
-          </cell>
-          <cell r="D79">
-            <v>-751.71999999999935</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80" t="str">
-            <v>2025-11-20</v>
-          </cell>
-          <cell r="B80">
-            <v>1</v>
-          </cell>
-          <cell r="C80">
-            <v>11910.93</v>
-          </cell>
-          <cell r="D80">
-            <v>-781.48999999999978</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81" t="str">
-            <v>2025-11-21</v>
-          </cell>
-          <cell r="B81">
-            <v>1</v>
-          </cell>
-          <cell r="C81">
-            <v>11914.67</v>
-          </cell>
-          <cell r="D81">
-            <v>-777.75</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82" t="str">
-            <v>2025-11-24</v>
-          </cell>
-          <cell r="B82">
-            <v>1</v>
-          </cell>
-          <cell r="C82">
-            <v>11971.4</v>
-          </cell>
-          <cell r="D82">
-            <v>-721.02000000000044</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83" t="str">
-            <v>2025-11-25</v>
-          </cell>
-          <cell r="B83">
-            <v>1</v>
-          </cell>
-          <cell r="C83">
-            <v>11988.32</v>
-          </cell>
-          <cell r="D83">
-            <v>-704.10000000000036</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84" t="str">
-            <v>2025-11-26</v>
-          </cell>
-          <cell r="B84">
-            <v>1</v>
-          </cell>
-          <cell r="C84">
-            <v>11936.89</v>
-          </cell>
-          <cell r="D84">
-            <v>-755.53000000000065</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85" t="str">
-            <v>2025-11-27</v>
-          </cell>
-          <cell r="B85">
-            <v>1</v>
-          </cell>
-          <cell r="C85">
-            <v>11881.6</v>
-          </cell>
-          <cell r="D85">
-            <v>-810.81999999999971</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86" t="str">
-            <v>2025-11-28</v>
-          </cell>
-          <cell r="B86">
-            <v>1</v>
-          </cell>
-          <cell r="C86">
-            <v>11902.3</v>
-          </cell>
-          <cell r="D86">
-            <v>-790.1200000000008</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87" t="str">
-            <v>2025-12-01</v>
-          </cell>
-          <cell r="B87">
-            <v>1</v>
-          </cell>
-          <cell r="C87">
-            <v>11940.95</v>
-          </cell>
-          <cell r="D87">
-            <v>-751.46999999999935</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88" t="str">
-            <v>2025-12-02</v>
-          </cell>
-          <cell r="B88">
-            <v>1</v>
-          </cell>
-          <cell r="C88">
-            <v>11895.57</v>
-          </cell>
-          <cell r="D88">
-            <v>-796.85000000000036</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89" t="str">
-            <v>2025-12-03</v>
-          </cell>
-          <cell r="B89">
-            <v>1</v>
-          </cell>
-          <cell r="C89">
-            <v>11880.93</v>
-          </cell>
-          <cell r="D89">
-            <v>-811.48999999999978</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90" t="str">
-            <v>2025-12-04</v>
-          </cell>
-          <cell r="B90">
-            <v>1</v>
-          </cell>
-          <cell r="C90">
-            <v>11912.38</v>
-          </cell>
-          <cell r="D90">
-            <v>-780.04000000000087</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91" t="str">
-            <v>2025-12-05</v>
-          </cell>
-          <cell r="B91">
-            <v>1</v>
-          </cell>
-          <cell r="C91">
-            <v>11963.23</v>
-          </cell>
-          <cell r="D91">
-            <v>-729.19000000000051</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92" t="str">
-            <v>2025-12-09</v>
-          </cell>
-          <cell r="B92">
-            <v>1</v>
-          </cell>
-          <cell r="C92">
-            <v>11990.09</v>
-          </cell>
-          <cell r="D92">
-            <v>-702.32999999999993</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93" t="str">
-            <v>2025-12-10</v>
-          </cell>
-          <cell r="B93">
-            <v>1</v>
-          </cell>
-          <cell r="C93">
-            <v>12003.18</v>
-          </cell>
-          <cell r="D93">
-            <v>-689.23999999999978</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94" t="str">
-            <v>2025-12-11</v>
-          </cell>
-          <cell r="B94">
-            <v>1</v>
-          </cell>
-          <cell r="C94">
-            <v>12020.9</v>
-          </cell>
-          <cell r="D94">
-            <v>-671.52000000000044</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95" t="str">
-            <v>2025-12-12</v>
-          </cell>
-          <cell r="B95">
-            <v>1</v>
-          </cell>
-          <cell r="C95">
-            <v>12047.45</v>
-          </cell>
-          <cell r="D95">
-            <v>-644.96999999999935</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96" t="str">
-            <v>2025-12-15</v>
-          </cell>
-          <cell r="B96">
-            <v>1</v>
-          </cell>
-          <cell r="C96">
-            <v>12097.93</v>
-          </cell>
-          <cell r="D96">
-            <v>-594.48999999999978</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97" t="str">
-            <v>2025-12-16</v>
-          </cell>
-          <cell r="B97">
-            <v>1</v>
-          </cell>
-          <cell r="C97">
-            <v>12130.01</v>
-          </cell>
-          <cell r="D97">
-            <v>-562.40999999999985</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98" t="str">
-            <v>2025-12-17</v>
-          </cell>
-          <cell r="B98">
-            <v>1</v>
-          </cell>
-          <cell r="C98">
-            <v>12105.56</v>
-          </cell>
-          <cell r="D98">
-            <v>-586.86000000000058</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99" t="str">
-            <v>2025-12-18</v>
-          </cell>
-          <cell r="B99">
-            <v>1</v>
-          </cell>
-          <cell r="C99">
-            <v>12059.78</v>
-          </cell>
-          <cell r="D99">
-            <v>-632.63999999999942</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100" t="str">
-            <v>2025-12-19</v>
-          </cell>
-          <cell r="B100">
-            <v>1</v>
-          </cell>
-          <cell r="C100">
-            <v>12021.61</v>
-          </cell>
-          <cell r="D100">
-            <v>-670.80999999999949</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101" t="str">
-            <v>2025-12-22</v>
-          </cell>
-          <cell r="B101">
-            <v>1</v>
-          </cell>
-          <cell r="C101">
-            <v>11996.14</v>
-          </cell>
-          <cell r="D101">
-            <v>-696.28000000000065</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102" t="str">
-            <v>2025-12-23</v>
-          </cell>
-          <cell r="B102">
-            <v>1</v>
-          </cell>
-          <cell r="C102">
-            <v>12010.43</v>
-          </cell>
-          <cell r="D102">
-            <v>-681.98999999999978</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>2025-12-24</v>
-          </cell>
-          <cell r="B103">
-            <v>1</v>
-          </cell>
-          <cell r="C103">
-            <v>12052.33</v>
-          </cell>
-          <cell r="D103">
-            <v>-640.09000000000015</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104" t="str">
-            <v>2025-12-25</v>
-          </cell>
-          <cell r="B104">
-            <v>1</v>
-          </cell>
-          <cell r="C104">
-            <v>12067.6</v>
-          </cell>
-          <cell r="D104">
-            <v>-624.81999999999971</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105" t="str">
-            <v>2025-12-26</v>
-          </cell>
-          <cell r="B105">
-            <v>1</v>
-          </cell>
-          <cell r="C105">
-            <v>12078.47</v>
-          </cell>
-          <cell r="D105">
-            <v>-613.95000000000073</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106" t="str">
-            <v>2025-12-29</v>
-          </cell>
-          <cell r="B106">
-            <v>1</v>
-          </cell>
-          <cell r="C106">
-            <v>12057.32</v>
-          </cell>
-          <cell r="D106">
-            <v>-635.10000000000036</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107" t="str">
-            <v>2025-12-30</v>
-          </cell>
-          <cell r="B107">
-            <v>1</v>
-          </cell>
-          <cell r="C107">
-            <v>12025.33</v>
-          </cell>
-          <cell r="D107">
-            <v>-667.09000000000015</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2284,8 +900,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3457,6 +2073,380 @@
         <v>14162.23</v>
       </c>
     </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="5">
+        <v>11960.18</v>
+      </c>
+      <c r="C107" s="6">
+        <v>13761.38</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="5">
+        <v>11989.46</v>
+      </c>
+      <c r="C108" s="6">
+        <v>13815.45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="5">
+        <v>11942.21</v>
+      </c>
+      <c r="C109" s="6">
+        <v>13743.1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="5">
+        <v>11886.72</v>
+      </c>
+      <c r="C110" s="6">
+        <v>13717.27</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" s="5">
+        <v>11915.64</v>
+      </c>
+      <c r="C111" s="6">
+        <v>13749.46</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" s="5">
+        <v>11952.1</v>
+      </c>
+      <c r="C112" s="6">
+        <v>13779.58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="5">
+        <v>11934.61</v>
+      </c>
+      <c r="C113" s="6">
+        <v>13788.05</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="5">
+        <v>11889.95</v>
+      </c>
+      <c r="C114" s="6">
+        <v>13717.44</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="5">
+        <v>11948.58</v>
+      </c>
+      <c r="C115" s="6">
+        <v>13793.44</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" s="5">
+        <v>11937.89</v>
+      </c>
+      <c r="C116" s="6">
+        <v>13769.16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" s="5">
+        <v>11891.18</v>
+      </c>
+      <c r="C117" s="6">
+        <v>13753.34</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" s="5">
+        <v>11857.35</v>
+      </c>
+      <c r="C118" s="6">
+        <v>13746.23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="5">
+        <v>11820.4</v>
+      </c>
+      <c r="C119" s="6">
+        <v>13684.48</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="5">
+        <v>11794.88</v>
+      </c>
+      <c r="C120" s="6">
+        <v>13685.6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="5">
+        <v>11847.16</v>
+      </c>
+      <c r="C121" s="6">
+        <v>13843.41</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" s="5">
+        <v>11853.55</v>
+      </c>
+      <c r="C122" s="6">
+        <v>13869.84</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="5">
+        <v>11818.07</v>
+      </c>
+      <c r="C123" s="6">
+        <v>13788.14</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="5">
+        <v>11778.52</v>
+      </c>
+      <c r="C124" s="6">
+        <v>13733.75</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" s="5">
+        <v>11823.69</v>
+      </c>
+      <c r="C125" s="6">
+        <v>13797.06</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" s="5">
+        <v>11801.23</v>
+      </c>
+      <c r="C126" s="6">
+        <v>13737.81</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="5">
+        <v>11820.48</v>
+      </c>
+      <c r="C127" s="6">
+        <v>13766.13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" s="5">
+        <v>11813.09</v>
+      </c>
+      <c r="C128" s="6">
+        <v>13677.2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" s="5">
+        <v>11795</v>
+      </c>
+      <c r="C129" s="6">
+        <v>13698.71</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" s="5">
+        <v>11785.3</v>
+      </c>
+      <c r="C130" s="6">
+        <v>13695.7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B131" s="5">
+        <v>11789.33</v>
+      </c>
+      <c r="C131" s="6">
+        <v>13702.74</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B132" s="5">
+        <v>11813.21</v>
+      </c>
+      <c r="C132" s="6">
+        <v>13719.86</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B133" s="5">
+        <v>11797.92</v>
+      </c>
+      <c r="C133" s="6">
+        <v>13739.86</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B134" s="5">
+        <v>11783.47</v>
+      </c>
+      <c r="C134" s="6">
+        <v>13688.86</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" s="5">
+        <v>11765.76</v>
+      </c>
+      <c r="C135" s="6">
+        <v>13638.87</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B136" s="5">
+        <v>11765.21</v>
+      </c>
+      <c r="C136" s="6">
+        <v>13586.46</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B137" s="5">
+        <v>11774.92</v>
+      </c>
+      <c r="C137" s="6">
+        <v>13588.26</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B138" s="5">
+        <v>11797.46</v>
+      </c>
+      <c r="C138" s="6">
+        <v>13608.37</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B139" s="5">
+        <v>11833.37</v>
+      </c>
+      <c r="C139" s="6">
+        <v>13577.61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B140" s="5">
+        <v>11839.59</v>
+      </c>
+      <c r="C140" s="6">
+        <v>13569.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
